--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -618,7 +618,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationStatement_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
 </t>
   </si>
   <si>
